--- a/olympic_simulator/media/simulacion_AFC Champions League Two_1880.xlsx
+++ b/olympic_simulator/media/simulacion_AFC Champions League Two_1880.xlsx
@@ -489,29 +489,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -520,29 +520,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -551,29 +551,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -582,29 +582,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>11</v>
-      </c>
       <c r="I6" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="9">
@@ -639,34 +639,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -675,16 +675,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -693,160 +693,160 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -926,29 +926,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>24</v>
       </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>19</v>
-      </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -957,29 +957,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -988,29 +988,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1032,16 +1032,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1063,16 +1063,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1081,29 +1081,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1112,29 +1112,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1143,29 +1143,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1178,25 +1178,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1205,29 +1205,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1249,16 +1249,16 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
         <v>11</v>
       </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>18</v>
-      </c>
-      <c r="H14" t="n">
-        <v>10</v>
-      </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1311,16 +1311,16 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1329,26 +1329,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
         <v>-1</v>
@@ -1360,29 +1360,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1391,29 +1391,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1441,10 +1441,10 @@
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1469,13 +1469,13 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1484,29 +1484,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
         <v>8</v>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>7</v>
       </c>
-      <c r="H21" t="n">
-        <v>8</v>
-      </c>
       <c r="I21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1515,29 +1515,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
         <v>8</v>
       </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>10</v>
       </c>
-      <c r="H22" t="n">
-        <v>13</v>
-      </c>
       <c r="I22" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1562,13 +1562,13 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="24">
@@ -1577,26 +1577,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1608,29 +1608,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I25" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bhayangkara Presisi Lampung FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1655,13 +1655,13 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="27">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Henan FC</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1686,10 +1686,10 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
         <v>5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>7</v>
       </c>
       <c r="I27" t="n">
         <v>-2</v>
@@ -1701,29 +1701,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="29">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1751,10 +1751,10 @@
         <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="30">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1779,13 +1779,13 @@
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="31">
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="32">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1841,13 +1841,13 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I32" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="33">
@@ -1856,26 +1856,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Philippines YNT FC</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I33" t="n">
         <v>-9</v>
@@ -1887,29 +1887,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="37">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2046,29 +2046,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2077,29 +2077,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="6">
@@ -2108,29 +2108,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="9">
@@ -2165,16 +2165,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -2183,106 +2183,106 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -2291,48 +2291,48 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2345,37 +2345,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Kazma SC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vakhsh Bokhtar</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bay Olympic FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>AL Hashemiya SC</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2452,29 +2452,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2483,29 +2483,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2514,29 +2514,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2545,29 +2545,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
@@ -2602,12 +2602,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2620,34 +2620,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -2656,48 +2656,48 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2710,106 +2710,106 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Kowloon City SC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Al Najma SC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quang Nam FC</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2889,29 +2889,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2936,13 +2936,13 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2951,29 +2951,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" t="n">
-        <v>12</v>
-      </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2982,26 +2982,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>-6</v>
@@ -3039,16 +3039,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -3057,16 +3057,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -3075,16 +3075,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3093,52 +3093,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3147,106 +3147,106 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lamphun Warriors FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Duhok SC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Malkiya SCC</t>
+          <t>Barkchi Hisor</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -3326,29 +3326,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3357,29 +3357,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
-        <v>8</v>
-      </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3388,29 +3388,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6">
@@ -3419,29 +3419,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="9">
@@ -3476,16 +3476,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -3494,34 +3494,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -3530,66 +3530,66 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3602,91 +3602,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shams Azar FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>FC Goa</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Wehdat SC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3763,29 +3763,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3794,29 +3794,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3825,29 +3825,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="6">
@@ -3856,29 +3856,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
@@ -3913,16 +3913,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3931,16 +3931,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -3949,52 +3949,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -4003,12 +4003,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4021,52 +4021,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -4075,12 +4075,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4093,16 +4093,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sukhothai FC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -4111,19 +4111,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Churchill Brothers FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Beijing Guoan FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4200,29 +4200,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -4231,29 +4231,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4262,29 +4262,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9</v>
-      </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4293,29 +4293,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
         <v>7</v>
       </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11</v>
-      </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="9">
@@ -4350,66 +4350,66 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4422,145 +4422,145 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dalian Yingbo FC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Samma FC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Sagesse SC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>PT Prachuap FC</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4637,29 +4637,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -4668,29 +4668,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
       <c r="I4" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -4699,29 +4699,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
-        <v>13</v>
-      </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6">
@@ -4730,29 +4730,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
@@ -4787,16 +4787,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -4805,66 +4805,66 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4877,127 +4877,127 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>One Taguig FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bengaluru FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5093,10 +5093,10 @@
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5121,10 +5121,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -5152,13 +5152,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5183,10 +5183,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5214,10 +5214,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5245,13 +5245,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5276,13 +5276,13 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5291,26 +5291,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -5322,29 +5322,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5369,10 +5369,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>-1</v>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5400,10 +5400,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>-1</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5431,10 +5431,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>-1</v>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5462,13 +5462,13 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5496,10 +5496,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5524,10 +5524,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>-2</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5596,102 +5596,102 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Al Wehdat SC</t>
+          <t>Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Bhayangkara Presisi Lampung FC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Al Nasr CSC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FC Istiklol Dushanbe</t>
+          <t>Al Najma SC BHR</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Al Riyadh FC</t>
+          <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Al Hilal Saudi FC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>Changchun Yatai FC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lee Man FC</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sharjah FC</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5704,34 +5704,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>Esteghlal FC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Auckland FC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chennaiyin FC</t>
+          <t>Khor Fakkan</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -5740,145 +5740,145 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Al Sadd SC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chabab SC Ghazieh</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Manama Club</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>FC Istiklol Dushanbe</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Geylang International FC</t>
-        </is>
-      </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Naft Al Basra SC</t>
+          <t>Quang Nam FC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Geylang International FC</t>
+          <t>Johor Darul Tazim FC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Al Rayyan SC</t>
+          <t>Auckland City FC</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kuala Lumpur City FC</t>
+          <t>Manama Club</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FC OKMK</t>
+          <t>Geylang International FC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
